--- a/Fase 2/Evidencias Proyecto/Evidencias de documentación/Sprint 2/Kanban-Board-S2.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de documentación/Sprint 2/Kanban-Board-S2.xlsx
@@ -585,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="40" customWidth="1" style="17" min="1" max="4"/>
@@ -604,7 +604,7 @@
     <row r="2" ht="15" customHeight="1" s="18">
       <c r="A2" s="20" t="inlineStr">
         <is>
-          <t>Período: 5 de octubre — 23 de octubre de 2026 (por confirmar)  |  Fecha de corte: 13 de octubre de 2026  |  Tablero en vivo: Trello "Capstone"</t>
+          <t>Período: 5 de octubre — 23 de octubre de 2026 (por confirmar)  |  Fecha de corte: 22 de octubre de 2026  |  Tablero en vivo: Trello "Capstone"</t>
         </is>
       </c>
     </row>
@@ -634,217 +634,227 @@
     <row r="5" ht="40" customHeight="1" s="18">
       <c r="A5" s="28" t="inlineStr">
         <is>
+          <t>S2 · Daily Meetings (Word)</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>MEJORA · Correcciones de la página
+(QA antes de producción · sin pts)</t>
+        </is>
+      </c>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>PENDIENTE · Configurar envío de correos (producción)
+(fuera de las historias · Christian)</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>PC-PRO-01
+Prospectos en lista y kanban (5 pts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1" s="18">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>S2 · Registro de Reuniones con la Agencia (Word)</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>MEJORA · Ajustes de identidad visual
+pedidos por la agencia (sin pts)</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="n"/>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>PC-PRO-02
+Registro manual de prospecto (2 pts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1" s="18">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>S2 · Acta de Sprint Review (Word)</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>PC-AUT-07
+Activación de cuenta del cliente (5 pts)</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="n"/>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>MEJORA · Correcciones de seguridad
+(panel interno y prospectos · sin pts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1" s="18">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>S2 · Acta de Sprint Retrospective (Word)</t>
+        </is>
+      </c>
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>S2 · Sprint Backlog (Excel)</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="n"/>
+      <c r="D8" s="28" t="inlineStr">
+        <is>
+          <t>MEJORA · Ajustes de la IA
+(rendimiento, texto limpio, pruebas · sin pts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1" s="18">
+      <c r="A9" s="28" t="n"/>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>S2 · Burndown (Excel)</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="n"/>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>PC-AUT-04
+Colaboradora solo ve sus clientes (8 pts) · GRUPAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1" s="18">
+      <c r="A10" s="28" t="n"/>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>S2 · Kanban Board (Excel)</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="n"/>
+      <c r="D10" s="28" t="inlineStr">
+        <is>
+          <t>PC-AUT-05
+Cliente solo ve su empresa (8 pts) · GRUPAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1" s="18">
+      <c r="A11" s="28" t="n"/>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>S2 · Impediment Log</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="n"/>
+      <c r="D11" s="28" t="inlineStr">
+        <is>
+          <t>PC-TEC-04
+Suite de pruebas de aislamiento (8 pts) · GRUPAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1" s="18">
+      <c r="A12" s="28" t="n"/>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>S2 · Incremento Funcional (Word)</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="n"/>
+      <c r="D12" s="28" t="inlineStr">
+        <is>
+          <t>PC-COT-01
+Cotizador en línea (8 pts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1" s="18">
+      <c r="A13" s="28" t="n"/>
+      <c r="B13" s="26" t="n"/>
+      <c r="C13" s="27" t="n"/>
+      <c r="D13" s="28" t="inlineStr">
+        <is>
+          <t>PC-COT-02
+Revisión de la cotización (5 pts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1" s="18">
+      <c r="A14" s="28" t="n"/>
+      <c r="B14" s="26" t="n"/>
+      <c r="C14" s="27" t="n"/>
+      <c r="D14" s="28" t="inlineStr">
+        <is>
+          <t>PC-CLI-01
+Conversión a cliente (5 pts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1" s="18">
+      <c r="A15" s="28" t="n"/>
+      <c r="B15" s="26" t="n"/>
+      <c r="C15" s="27" t="n"/>
+      <c r="D15" s="28" t="inlineStr">
+        <is>
+          <t>PC-CLI-02
+Ficha del cliente (8 pts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1" s="18">
+      <c r="A16" s="28" t="n"/>
+      <c r="B16" s="26" t="n"/>
+      <c r="C16" s="27" t="n"/>
+      <c r="D16" s="28" t="inlineStr">
+        <is>
+          <t>PC-IA-01
+Diagnóstico de cotización con IA (8 pts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1" s="18">
+      <c r="A17" s="28" t="n"/>
+      <c r="B17" s="26" t="n"/>
+      <c r="C17" s="27" t="n"/>
+      <c r="D17" s="28" t="inlineStr">
+        <is>
+          <t>PC-SEO-01b
+Metadatos del CMS publicados en el sitio (sin pts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1" s="18">
+      <c r="A18" s="28" t="n"/>
+      <c r="B18" s="26" t="n"/>
+      <c r="C18" s="27" t="n"/>
+      <c r="D18" s="28" t="inlineStr">
+        <is>
           <t>Modelo de Base de Datos · extensión
 (sin pts)</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
-        <is>
-          <t>MEJORA · Correcciones de la página
-(QA antes de producción · sin pts)</t>
-        </is>
-      </c>
-      <c r="C5" s="27" t="inlineStr">
-        <is>
-          <t>PC-AUT-04
-Colaboradora solo ve sus clientes (8 pts) · GRUPAL</t>
-        </is>
-      </c>
-      <c r="D5" s="28" t="inlineStr">
-        <is>
-          <t>PC-PRO-01
-Prospectos en lista y kanban (5 pts)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1" s="18">
-      <c r="A6" s="28" t="inlineStr">
-        <is>
-          <t>PC-AUT-05
-Cliente solo ve su empresa (8 pts) · GRUPAL</t>
-        </is>
-      </c>
-      <c r="B6" s="26" t="inlineStr">
-        <is>
-          <t>MEJORA · Ajustes de identidad visual
-pedidos por la agencia (sin pts)</t>
-        </is>
-      </c>
-      <c r="C6" s="27" t="inlineStr">
-        <is>
-          <t>PC-CLI-01
-Conversión a cliente (5 pts)</t>
-        </is>
-      </c>
-      <c r="D6" s="28" t="inlineStr">
-        <is>
-          <t>PC-PRO-02
-Registro manual de prospecto (2 pts)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="40" customHeight="1" s="18">
-      <c r="A7" s="28" t="inlineStr">
-        <is>
-          <t>PC-TEC-04
-Suite de pruebas de aislamiento (8 pts) · GRUPAL</t>
-        </is>
-      </c>
-      <c r="B7" s="26" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="28" t="inlineStr">
-        <is>
-          <t>MEJORA · Correcciones de seguridad
-(panel interno y prospectos · sin pts)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="40" customHeight="1" s="18">
-      <c r="A8" s="28" t="inlineStr">
-        <is>
-          <t>PC-SEO-01b
-Metadatos del CMS publicados en el sitio (sin pts)</t>
-        </is>
-      </c>
-      <c r="B8" s="26" t="n"/>
-      <c r="C8" s="27" t="n"/>
-      <c r="D8" s="28" t="inlineStr">
-        <is>
-          <t>MEJORA · Ajustes de la IA
-(rendimiento, texto limpio, pruebas · sin pts)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="40" customHeight="1" s="18">
-      <c r="A9" s="28" t="inlineStr">
-        <is>
-          <t>PC-COT-01
-Cotizador en línea (8 pts)</t>
-        </is>
-      </c>
-      <c r="B9" s="26" t="n"/>
-      <c r="C9" s="27" t="n"/>
-      <c r="D9" s="28" t="n"/>
-    </row>
-    <row r="10" ht="40" customHeight="1" s="18">
-      <c r="A10" s="28" t="inlineStr">
-        <is>
-          <t>PC-COT-02
-Revisión de la cotización (5 pts)</t>
-        </is>
-      </c>
-      <c r="B10" s="26" t="n"/>
-      <c r="C10" s="27" t="n"/>
-      <c r="D10" s="28" t="n"/>
-    </row>
-    <row r="11" ht="40" customHeight="1" s="18">
-      <c r="A11" s="28" t="inlineStr">
-        <is>
-          <t>PC-CLI-02
-Ficha del cliente (8 pts)</t>
-        </is>
-      </c>
-      <c r="B11" s="26" t="n"/>
-      <c r="C11" s="27" t="n"/>
-      <c r="D11" s="28" t="n"/>
-    </row>
-    <row r="12" ht="40" customHeight="1" s="18">
-      <c r="A12" s="28" t="inlineStr">
-        <is>
-          <t>PC-IA-01
-Diagnóstico de cotización con IA (8 pts)</t>
-        </is>
-      </c>
-      <c r="B12" s="26" t="n"/>
-      <c r="C12" s="27" t="n"/>
-      <c r="D12" s="28" t="n"/>
-    </row>
-    <row r="13" ht="40" customHeight="1" s="18">
-      <c r="A13" s="28" t="inlineStr">
-        <is>
-          <t>S2 · Sprint Backlog (Excel)</t>
-        </is>
-      </c>
-      <c r="B13" s="26" t="n"/>
-      <c r="C13" s="27" t="n"/>
-      <c r="D13" s="28" t="n"/>
-    </row>
-    <row r="14" ht="40" customHeight="1" s="18">
-      <c r="A14" s="28" t="inlineStr">
-        <is>
-          <t>S2 · Burndown (Excel)</t>
-        </is>
-      </c>
-      <c r="B14" s="26" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="D14" s="28" t="n"/>
-    </row>
-    <row r="15" ht="40" customHeight="1" s="18">
-      <c r="A15" s="28" t="inlineStr">
-        <is>
-          <t>S2 · Kanban Board (Excel)</t>
-        </is>
-      </c>
-      <c r="B15" s="26" t="n"/>
-      <c r="C15" s="27" t="n"/>
-      <c r="D15" s="28" t="n"/>
-    </row>
-    <row r="16" ht="40" customHeight="1" s="18">
-      <c r="A16" s="28" t="inlineStr">
-        <is>
-          <t>S2 · Daily Meetings (Word)</t>
-        </is>
-      </c>
-      <c r="B16" s="26" t="n"/>
-      <c r="C16" s="27" t="n"/>
-      <c r="D16" s="28" t="n"/>
-    </row>
-    <row r="17" ht="40" customHeight="1" s="18">
-      <c r="A17" s="28" t="inlineStr">
-        <is>
-          <t>S2 · Impediment Log</t>
-        </is>
-      </c>
-      <c r="B17" s="26" t="n"/>
-      <c r="C17" s="27" t="n"/>
-      <c r="D17" s="28" t="n"/>
-    </row>
-    <row r="18" ht="40" customHeight="1" s="18">
-      <c r="A18" s="28" t="inlineStr">
-        <is>
-          <t>S2 · Registro de Reuniones con la Agencia (Word)</t>
-        </is>
-      </c>
-      <c r="B18" s="26" t="n"/>
-      <c r="C18" s="27" t="n"/>
-      <c r="D18" s="28" t="n"/>
     </row>
     <row r="19" ht="40" customHeight="1" s="18">
-      <c r="A19" s="28" t="inlineStr">
-        <is>
-          <t>S2 · Incremento Funcional (Word)</t>
-        </is>
-      </c>
+      <c r="A19" s="28" t="n"/>
       <c r="B19" s="26" t="n"/>
       <c r="C19" s="27" t="n"/>
       <c r="D19" s="28" t="n"/>
     </row>
     <row r="20" ht="40" customHeight="1" s="18">
-      <c r="A20" s="28" t="inlineStr">
-        <is>
-          <t>S2 · Acta de Sprint Review (Word)</t>
-        </is>
-      </c>
+      <c r="A20" s="28" t="n"/>
       <c r="B20" s="26" t="n"/>
       <c r="C20" s="27" t="n"/>
       <c r="D20" s="28" t="n"/>
     </row>
     <row r="21" ht="40" customHeight="1" s="18">
-      <c r="A21" s="28" t="inlineStr">
-        <is>
-          <t>S2 · Acta de Sprint Retrospective (Word)</t>
-        </is>
-      </c>
+      <c r="A21" s="28" t="n"/>
       <c r="B21" s="26" t="n"/>
       <c r="C21" s="27" t="n"/>
       <c r="D21" s="28" t="n"/>
@@ -986,7 +996,13 @@
         </is>
       </c>
     </row>
-    <row r="44" s="18"/>
+    <row r="44" ht="110" customHeight="1" s="18">
+      <c r="A44" s="36" t="inlineStr">
+        <is>
+          <t>• Corte 22 oct: en la reunión interna del martes 20 oct (Felipe, Esteban y Christian) se dieron por Hecho las tarjetas que estaban En revisión: PC-AUT-04, PC-AUT-05, PC-TEC-04, PC-COT-01, PC-COT-02, PC-CLI-01, PC-CLI-02, PC-SEO-01b y Modelo de Base de Datos · extensión; se movieron en Trello el 22 oct. PC-IA-01 se registra Hecha (técnicamente lista; ver Impediment Log I-007 por el cobro de la API de Gemini). PC-AUT-07 se incorpora a En proceso (compromiso 65 → 70 pts). «PENDIENTE · Configurar envío de correos» queda En revisión, a cargo de Christian. Las tarjetas PC-IA-01, PC-AUT-07 y las dos MEJORA de Hecho (12 oct) se crearon en Trello el 22 oct. Tablero: 4 / 8 / 1 / 14 → 27 tarjetas.</t>
+        </is>
+      </c>
+    </row>
     <row r="45" s="18"/>
     <row r="46" s="18"/>
     <row r="47" s="18"/>
@@ -1004,7 +1020,7 @@
     <row r="59" s="18"/>
     <row r="60" s="18"/>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A40:D40"/>
     <mergeCell ref="A38:D38"/>
@@ -1013,6 +1029,7 @@
     <mergeCell ref="A41:D41"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A44:D44"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
